--- a/data/trans_orig/Q64A_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q64A_R-Clase-trans_orig.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio que lleva trabajando en su empresa (en meses)</t>
+          <t>Tiempo medio que lleva trabajando en su empresa (en meses) (tasa de respuesta: 97,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>109,94; 132,64</t>
+          <t>109,98; 132,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>138,5; 168,61</t>
+          <t>139,06; 171,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>121,82; 151,74</t>
+          <t>122,09; 150,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>152,52; 182,23</t>
+          <t>152,73; 182,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,46; 123,39</t>
+          <t>92,15; 121,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,64; 123,89</t>
+          <t>95,08; 124,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>108,78; 139,2</t>
+          <t>109,85; 138,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>136,02; 162,05</t>
+          <t>136,93; 161,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>105,96; 125,0</t>
+          <t>106,94; 125,29</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>124,56; 147,1</t>
+          <t>124,02; 146,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>120,91; 141,39</t>
+          <t>120,19; 141,26</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>148,42; 168,39</t>
+          <t>147,45; 167,94</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>109,86; 140,09</t>
+          <t>109,87; 140,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>129,48; 158,56</t>
+          <t>131,45; 160,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>118,0; 147,32</t>
+          <t>117,93; 148,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>146,79; 180,77</t>
+          <t>146,96; 181,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>54,47; 73,86</t>
+          <t>55,21; 73,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,98; 125,11</t>
+          <t>88,77; 122,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,74; 133,65</t>
+          <t>96,58; 131,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>113,98; 138,3</t>
+          <t>114,33; 138,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>87,16; 106,63</t>
+          <t>87,1; 106,6</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>117,26; 139,86</t>
+          <t>118,11; 141,5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>113,92; 137,26</t>
+          <t>112,73; 136,35</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>135,97; 157,17</t>
+          <t>135,71; 157,95</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>104,63; 126,97</t>
+          <t>105,52; 127,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>115,78; 144,83</t>
+          <t>115,65; 144,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>131,19; 164,54</t>
+          <t>129,49; 163,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,66; 159,91</t>
+          <t>19,77; 162,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52,03; 93,91</t>
+          <t>51,11; 92,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>84,27; 114,62</t>
+          <t>84,42; 114,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>89,31; 135,0</t>
+          <t>90,39; 134,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>132,62; 188,27</t>
+          <t>136,26; 190,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>100,13; 120,02</t>
+          <t>98,96; 120,08</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>109,84; 133,07</t>
+          <t>109,61; 131,62</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>124,35; 151,77</t>
+          <t>124,37; 151,9</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,64; 160,6</t>
+          <t>29,19; 161,62</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>88,01; 103,7</t>
+          <t>87,87; 103,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94,91; 117,27</t>
+          <t>94,84; 116,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89,67; 109,52</t>
+          <t>89,36; 108,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>118,61; 141,02</t>
+          <t>118,7; 141,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>53,9; 75,05</t>
+          <t>53,62; 73,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,95; 68,99</t>
+          <t>52,23; 69,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,06; 76,76</t>
+          <t>60,65; 76,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>89,47; 105,89</t>
+          <t>89,83; 105,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>79,74; 92,31</t>
+          <t>79,48; 92,3</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79,28; 94,9</t>
+          <t>79,58; 93,73</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78,73; 92,19</t>
+          <t>79,27; 92,19</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>109,09; 124,05</t>
+          <t>108,54; 122,83</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1276,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>54,53; 78,54</t>
+          <t>54,93; 76,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79,83; 114,26</t>
+          <t>79,59; 114,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69,99; 103,21</t>
+          <t>69,62; 103,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86,48; 116,88</t>
+          <t>84,37; 114,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>55,14; 78,96</t>
+          <t>54,35; 79,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,1; 100,46</t>
+          <t>69,08; 98,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,13; 84,99</t>
+          <t>62,96; 85,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>59,64; 95,79</t>
+          <t>57,78; 96,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>57,6; 73,83</t>
+          <t>57,32; 74,09</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76,58; 101,29</t>
+          <t>77,86; 100,67</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69,83; 89,04</t>
+          <t>69,31; 89,58</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>68,57; 99,64</t>
+          <t>70,19; 99,12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1348,62 +1348,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>105,48</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>126,04</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>116,93</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>125,0</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>72,89</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>86,23</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>91,63</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>113,04</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>94,11</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>110,09</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>106,26</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>120,01</t>
         </is>
       </c>
     </row>
@@ -1416,221 +1416,80 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>100,49; 110,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>120,49; 133,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>110,9; 122,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>84,18; 145,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>67,59; 78,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>80,36; 93,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>85,33; 97,33</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>100,9; 120,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>90,43; 97,96</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>105,55; 114,71</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>101,98; 110,51</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>92,12; 131,78</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>105,48</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>126,04</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>116,93</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>125,0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>72,89</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>86,23</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>91,63</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>113,04</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>94,11</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>110,09</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>106,26</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>120,01</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>100,07; 110,71</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>120,03; 132,41</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>110,99; 123,09</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>73,93; 145,38</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>67,85; 78,58</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>80,29; 92,92</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>85,7; 97,78</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>100,18; 119,87</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>90,54; 98,24</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>105,29; 114,85</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>102,24; 110,64</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>94,34; 131,46</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>

--- a/data/trans_orig/Q64A_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q64A_R-Clase-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>167,13</t>
+          <t>161,17</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>148,92</t>
+          <t>150,85</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>158,5</t>
+          <t>156,32</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>109,98; 132,45</t>
+          <t>110,57; 134,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>139,06; 171,44</t>
+          <t>137,91; 167,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>122,09; 150,26</t>
+          <t>122,7; 150,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>152,73; 182,67</t>
+          <t>147,67; 175,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,15; 121,81</t>
+          <t>92,86; 122,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,08; 124,25</t>
+          <t>95,62; 125,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>109,85; 138,69</t>
+          <t>108,95; 138,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>136,93; 161,91</t>
+          <t>138,01; 162,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>106,94; 125,29</t>
+          <t>106,83; 124,61</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>124,02; 146,3</t>
+          <t>123,63; 147,69</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>120,19; 141,26</t>
+          <t>120,94; 142,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>147,45; 167,94</t>
+          <t>146,84; 166,26</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>163,83</t>
+          <t>161,84</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>126,06</t>
+          <t>125,24</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>146,81</t>
+          <t>145,12</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>109,87; 140,7</t>
+          <t>110,97; 139,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>131,45; 160,97</t>
+          <t>130,18; 159,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>117,93; 148,91</t>
+          <t>117,79; 147,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>146,96; 181,2</t>
+          <t>145,7; 177,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>55,21; 73,94</t>
+          <t>54,59; 74,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>88,77; 122,79</t>
+          <t>90,15; 122,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,58; 131,02</t>
+          <t>97,46; 132,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>114,33; 138,25</t>
+          <t>112,81; 137,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>87,1; 106,6</t>
+          <t>87,24; 107,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>118,11; 141,5</t>
+          <t>117,61; 141,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>112,73; 136,35</t>
+          <t>112,59; 135,58</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>135,71; 157,95</t>
+          <t>135,53; 156,09</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>77,45</t>
+          <t>151,62</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>160,74</t>
+          <t>156,85</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,96</t>
+          <t>152,82</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>105,52; 127,14</t>
+          <t>104,0; 125,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>115,65; 144,86</t>
+          <t>115,8; 145,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>129,49; 163,36</t>
+          <t>132,53; 163,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,77; 162,04</t>
+          <t>135,09; 168,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>51,11; 92,14</t>
+          <t>51,86; 93,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>84,42; 114,07</t>
+          <t>83,99; 114,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>90,39; 134,19</t>
+          <t>90,34; 134,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>136,26; 190,85</t>
+          <t>133,58; 184,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>98,96; 120,08</t>
+          <t>99,58; 119,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>109,61; 131,62</t>
+          <t>110,11; 132,35</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>124,37; 151,9</t>
+          <t>125,11; 152,66</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29,19; 161,62</t>
+          <t>139,24; 166,95</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>130,29</t>
+          <t>125,06</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>97,45</t>
+          <t>93,34</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>116,1</t>
+          <t>111,24</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>87,87; 103,98</t>
+          <t>87,03; 104,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94,84; 116,04</t>
+          <t>95,15; 116,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89,36; 108,78</t>
+          <t>88,3; 109,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>118,7; 141,41</t>
+          <t>115,06; 134,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>53,62; 73,17</t>
+          <t>53,76; 73,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,23; 69,46</t>
+          <t>51,94; 68,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,65; 76,09</t>
+          <t>61,25; 76,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>89,83; 105,72</t>
+          <t>85,99; 100,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>79,48; 92,3</t>
+          <t>79,5; 92,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79,58; 93,73</t>
+          <t>79,22; 94,02</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79,27; 92,19</t>
+          <t>78,84; 91,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>108,54; 122,83</t>
+          <t>104,27; 116,99</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>100,37</t>
+          <t>89,11</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>79,28</t>
+          <t>85,67</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>88,04</t>
+          <t>87,39</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>54,93; 76,55</t>
+          <t>55,12; 77,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79,59; 114,05</t>
+          <t>78,2; 114,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69,62; 103,51</t>
+          <t>70,68; 103,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84,37; 114,98</t>
+          <t>78,47; 102,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>54,35; 79,93</t>
+          <t>54,48; 79,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,08; 98,68</t>
+          <t>68,61; 100,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,96; 85,83</t>
+          <t>62,73; 85,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>57,78; 96,26</t>
+          <t>77,04; 94,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>57,32; 74,09</t>
+          <t>57,5; 74,1</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77,86; 100,67</t>
+          <t>78,09; 101,94</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69,31; 89,58</t>
+          <t>69,73; 89,54</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>70,19; 99,12</t>
+          <t>80,07; 95,97</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>125,0</t>
+          <t>136,61</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>113,04</t>
+          <t>114,27</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>120,01</t>
+          <t>126,86</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>100,49; 110,95</t>
+          <t>99,89; 110,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>120,49; 133,35</t>
+          <t>119,12; 132,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>110,9; 122,97</t>
+          <t>111,33; 123,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84,18; 145,12</t>
+          <t>130,56; 142,85</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>67,59; 78,73</t>
+          <t>67,54; 78,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>80,36; 93,07</t>
+          <t>80,14; 92,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>85,33; 97,33</t>
+          <t>85,95; 98,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>100,9; 120,04</t>
+          <t>109,26; 119,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>90,43; 97,96</t>
+          <t>90,72; 98,27</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>105,55; 114,71</t>
+          <t>105,17; 114,86</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>101,98; 110,51</t>
+          <t>102,29; 110,95</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>92,12; 131,78</t>
+          <t>122,96; 130,71</t>
         </is>
       </c>
     </row>
